--- a/src/pandorafits/formats/visda/level2-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level2-ffi_visda.xlsx
@@ -15,6 +15,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext4" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext5" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext6" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext7" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext8" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,12 +502,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>ASTROMETRY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CompImageHDU</t>
+          <t>BinTableHDU</t>
         </is>
       </c>
       <c r="C5" t="b">
@@ -515,12 +517,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CATALOG</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BinTableHDU</t>
+          <t>CompImageHDU</t>
         </is>
       </c>
       <c r="C6" t="b">
@@ -530,12 +532,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PRF_MODEL</t>
+          <t>CATALOG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CompImageHDU</t>
+          <t>BinTableHDU</t>
         </is>
       </c>
       <c r="C7" t="b">
@@ -545,7 +547,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>APERTURE</t>
+          <t>PRF_MODEL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -555,6 +557,292 @@
       </c>
       <c r="C8" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>APERTURE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CompImageHDU</t>
+        </is>
+      </c>
+      <c r="C9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ImageHDU</t>
+        </is>
+      </c>
+      <c r="C10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fixed Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Example Value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>XTENSION</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Image extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BITPIX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>-64</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-64</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>array data type</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NAXIS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>number of array dimensions</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NAXIS1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NAXIS2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NAXIS3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PCOUNT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>number of parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GCOUNT</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>number of groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>UNIT</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>electrons/pixel</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>data units: electrons/pixel</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ZplUfmkRZmkRdmkR</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-07T16:22:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>606763591</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-07T16:22:35</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -568,7 +856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -705,11 +993,7 @@
           <t>NEXTEND</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>3</t>
@@ -868,7 +1152,7 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -886,7 +1170,7 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -904,7 +1188,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LTT_1445</t>
+          <t>Dark</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -922,7 +1206,7 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2025-12-03__17-33-04.907_VisImg_LTT_1445_d1024x1024x0001_b1_e000200000us.sp</t>
+          <t>/sssp/data/2025/12/03/2025-12-03__15-00-08_VisImg_Dark_d1024x1024x0010_b1_e000200000us.sp</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1084,7 +1368,7 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1102,7 +1386,7 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1138,7 +1422,7 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>818098421</t>
+          <t>818089246</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1156,7 +1440,7 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>907000000</t>
+          <t>182000000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1210,7 +1494,7 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1228,12 +1512,12 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>JaXEJVWEJZWEJZWE</t>
+          <t>aCRLc9PLaAPLa9PL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2025-12-31T11:13:55</t>
+          <t>HDU checksum updated 2026-01-07T16:22:34</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1535,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2025-12-31T11:13:55</t>
+          <t>data unit checksum updated 2026-01-07T16:22:34</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1562,7 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>45.46099853515625</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1296,7 +1580,7 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>-16.594999313354492</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1314,7 +1598,7 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1326,13 +1610,13 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>GAIA_ID</t>
+          <t>PFCLASS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5153091836072107136</t>
+          <t>VISDAFFILevel2HDUList</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -1340,13 +1624,13 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>GAIA_ID</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cast data to float.</t>
+          <t>2738188646457069696</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -1360,7 +1644,7 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Applied bias.</t>
+          <t>Cast data to float.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1374,7 +1658,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Applied dark.</t>
+          <t>Applied bias.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1388,7 +1672,7 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Applied flat.</t>
+          <t>Applied dark.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1402,7 +1686,7 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Applied gain.</t>
+          <t>Applied flat.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1416,10 +1700,24 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
+          <t>Applied gain.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
           <t>Appended WCS.</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1432,7 +1730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1560,7 +1858,7 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1632,10 +1930,14 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HPMGIPJ9HPJGHPJ9</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>9aGCEX9B9aGBCU9B</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-07T16:22:34</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1646,111 +1948,111 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1132213348</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>1137358662</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-07T16:22:34</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>WCSAXES</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>electrons/pixel</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Number of coordinate axes</t>
+          <t>data units: electrons/pixel</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CRPIX1</t>
+          <t>PFSOFTV</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1024.0</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Pixel coordinate of reference point</t>
-        </is>
-      </c>
+          <t>0.4.2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CRPIX2</t>
+          <t>WCSAXES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1024.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Pixel coordinate of reference point</t>
+          <t>Number of coordinate axes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PC1_1</t>
+          <t>CRPIX1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.76604444311898</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Coordinate transformation matrix element</t>
+          <t>Pixel coordinate of reference point</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PC1_2</t>
+          <t>CRPIX2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.64278760968654</t>
+          <t>1024.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Coordinate transformation matrix element</t>
+          <t>Pixel coordinate of reference point</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PC2_1</t>
+          <t>PC1_1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.64278760968654</t>
+          <t>-0.76604444311898</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1762,13 +2064,13 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PC2_2</t>
+          <t>PC1_2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.76604444311898</t>
+          <t>-0.64278760968654</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1780,283 +2082,283 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CDELT1</t>
+          <t>PC2_1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.00021666666666666</t>
+          <t>-0.64278760968654</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[deg] Coordinate increment at reference point</t>
+          <t>Coordinate transformation matrix element</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CDELT2</t>
+          <t>PC2_2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.00021666666666667</t>
+          <t>0.76604444311898</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>[deg] Coordinate increment at reference point</t>
+          <t>Coordinate transformation matrix element</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CUNIT1</t>
+          <t>CDELT1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>-0.00021666666666666</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Units of coordinate increment and value</t>
+          <t>[deg] Coordinate increment at reference point</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CUNIT2</t>
+          <t>CDELT2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>0.00021666666666667</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Units of coordinate increment and value</t>
+          <t>[deg] Coordinate increment at reference point</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CTYPE1</t>
+          <t>CUNIT1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RA---TAN-SIP</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>TAN (gnomonic) projection + SIP distortions</t>
+          <t>Units of coordinate increment and value</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CTYPE2</t>
+          <t>CUNIT2</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DEC--TAN-SIP</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>TAN (gnomonic) projection + SIP distortions</t>
+          <t>Units of coordinate increment and value</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CRVAL1</t>
+          <t>CTYPE1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>45.460998535156</t>
+          <t>RA---TAN-SIP</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>[deg] Coordinate value at reference point</t>
+          <t>TAN (gnomonic) projection + SIP distortions</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CRVAL2</t>
+          <t>CTYPE2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-16.594999313354</t>
+          <t>DEC--TAN-SIP</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[deg] Coordinate value at reference point</t>
+          <t>TAN (gnomonic) projection + SIP distortions</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LONPOLE</t>
+          <t>CRVAL1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>180.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[deg] Native longitude of celestial pole</t>
+          <t>[deg] Coordinate value at reference point</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LATPOLE</t>
+          <t>CRVAL2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-16.594999313354</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[deg] Native latitude of celestial pole</t>
+          <t>[deg] Coordinate value at reference point</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MJDREF</t>
+          <t>LONPOLE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>180.0</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[d] MJD of fiducial time</t>
+          <t>[deg] Native longitude of celestial pole</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RADESYS</t>
+          <t>LATPOLE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ICRS</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Equatorial coordinate system</t>
+          <t>[deg] Native latitude of celestial pole</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A_ORDER</t>
+          <t>MJDREF</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SIP polynomial order, axis 0, detector to sky</t>
+          <t>[d] MJD of fiducial time</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A_0_0</t>
+          <t>RADESYS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3.37003854432842e-18</t>
+          <t>ICRS</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>Equatorial coordinate system</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A_0_1</t>
+          <t>A_ORDER</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>-6.9785263260057e-20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>SIP polynomial order, axis 0, detector to sky</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A_0_2</t>
+          <t>A_0_0</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>-3.9703987595512e-23</t>
+          <t>3.37003854432842e-18</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2068,13 +2370,13 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A_0_3</t>
+          <t>A_0_1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>6.66363813187626e-25</t>
+          <t>-6.9785263260057e-20</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2086,13 +2388,13 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A_1_0</t>
+          <t>A_0_2</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>-1.6079633451011e-05</t>
+          <t>-3.9703987595512e-23</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2104,13 +2406,13 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A_1_1</t>
+          <t>A_0_3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>-8.2922292375176e-07</t>
+          <t>6.66363813187626e-25</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2122,13 +2424,13 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A_1_2</t>
+          <t>A_1_0</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>-3.3183151069542e-10</t>
+          <t>-1.6079633451011e-05</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2140,13 +2442,13 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A_2_0</t>
+          <t>A_1_1</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>-5.6509448985679e-23</t>
+          <t>-8.2922292375176e-07</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2158,13 +2460,13 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A_2_1</t>
+          <t>A_1_2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1.22485736636324e-24</t>
+          <t>-3.3183151069542e-10</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2176,13 +2478,13 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A_3_0</t>
+          <t>A_2_0</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-3.6017523652885e-10</t>
+          <t>-5.6509448985679e-23</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2194,31 +2496,31 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>B_ORDER</t>
+          <t>A_2_1</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1.22485736636324e-24</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>SIP polynomial order, axis 1, detector to sky</t>
+          <t>SIP distortion coefficient</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>B_0_0</t>
+          <t>A_3_0</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.000151435005371086</t>
+          <t>-3.6017523652885e-10</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2230,31 +2532,31 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>B_0_1</t>
+          <t>B_ORDER</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.000544760966309224</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>SIP polynomial order, axis 1, detector to sky</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>B_0_2</t>
+          <t>B_0_0</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1.36516576587348e-05</t>
+          <t>0.000151435005371086</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2266,13 +2568,13 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>B_0_3</t>
+          <t>B_0_1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1.09338166521394e-10</t>
+          <t>0.000544760966309224</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2284,13 +2586,13 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>B_1_0</t>
+          <t>B_0_2</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1.54376528535914e-18</t>
+          <t>1.36516576587348e-05</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2302,13 +2604,13 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>B_1_1</t>
+          <t>B_0_3</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>3.52359242917892e-20</t>
+          <t>1.09338166521394e-10</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2320,13 +2622,13 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>B_1_2</t>
+          <t>B_1_0</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>-2.4342035926037e-23</t>
+          <t>1.54376528535914e-18</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2338,13 +2640,13 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>B_2_0</t>
+          <t>B_1_1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1.44813947783169e-05</t>
+          <t>3.52359242917892e-20</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2356,13 +2658,13 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>B_2_1</t>
+          <t>B_1_2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>7.88636107165082e-11</t>
+          <t>-2.4342035926037e-23</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2374,13 +2676,13 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>B_3_0</t>
+          <t>B_2_0</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>-1.4166460599018e-23</t>
+          <t>1.44813947783169e-05</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2392,31 +2694,31 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AP_ORDER</t>
+          <t>B_2_1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7.88636107165082e-11</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>SIP polynomial order, axis 0, sky to detector</t>
+          <t>SIP distortion coefficient</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AP_0_0</t>
+          <t>B_3_0</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>-3.3700385443284e-18</t>
+          <t>-1.4166460599018e-23</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2428,31 +2730,31 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AP_0_1</t>
+          <t>AP_ORDER</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>6.9785263260057e-20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>SIP polynomial order, axis 0, sky to detector</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AP_0_2</t>
+          <t>AP_0_0</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>3.97039875955128e-23</t>
+          <t>-3.3700385443284e-18</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2464,13 +2766,13 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AP_0_3</t>
+          <t>AP_0_1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>-6.6636381318762e-25</t>
+          <t>6.9785263260057e-20</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2482,13 +2784,13 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AP_1_0</t>
+          <t>AP_0_2</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1.60796334510111e-05</t>
+          <t>3.97039875955128e-23</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2500,13 +2802,13 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AP_1_1</t>
+          <t>AP_0_3</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>8.29222923751763e-07</t>
+          <t>-6.6636381318762e-25</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2518,13 +2820,13 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AP_1_2</t>
+          <t>AP_1_0</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>3.31831510695423e-10</t>
+          <t>1.60796334510111e-05</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2536,13 +2838,13 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AP_2_0</t>
+          <t>AP_1_1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>5.65094489856793e-23</t>
+          <t>8.29222923751763e-07</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2554,13 +2856,13 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AP_2_1</t>
+          <t>AP_1_2</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>-1.2248573663632e-24</t>
+          <t>3.31831510695423e-10</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2572,13 +2874,13 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AP_3_0</t>
+          <t>AP_2_0</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>3.60175236528857e-10</t>
+          <t>5.65094489856793e-23</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2590,31 +2892,31 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BP_ORDER</t>
+          <t>AP_2_1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-1.2248573663632e-24</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>SIP polynomial order, axis 1, sky to detector</t>
+          <t>SIP distortion coefficient</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BP_0_0</t>
+          <t>AP_3_0</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>-0.00015143500537108</t>
+          <t>3.60175236528857e-10</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2626,31 +2928,31 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BP_0_1</t>
+          <t>BP_ORDER</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>-0.00054476096630922</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SIP distortion coefficient</t>
+          <t>SIP polynomial order, axis 1, sky to detector</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BP_0_2</t>
+          <t>BP_0_0</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>-1.3651657658734e-05</t>
+          <t>-0.00015143500537108</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2662,13 +2964,13 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BP_0_3</t>
+          <t>BP_0_1</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>-1.0933816652139e-10</t>
+          <t>-0.00054476096630922</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2680,13 +2982,13 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>BP_1_0</t>
+          <t>BP_0_2</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>-1.5437652853591e-18</t>
+          <t>-1.3651657658734e-05</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2698,13 +3000,13 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>BP_1_1</t>
+          <t>BP_0_3</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>-3.5235924291789e-20</t>
+          <t>-1.0933816652139e-10</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2716,13 +3018,13 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BP_1_2</t>
+          <t>BP_1_0</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2.43420359260379e-23</t>
+          <t>-1.5437652853591e-18</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2734,13 +3036,13 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BP_2_0</t>
+          <t>BP_1_1</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>-1.4481394778316e-05</t>
+          <t>-3.5235924291789e-20</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2752,13 +3054,13 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>BP_2_1</t>
+          <t>BP_1_2</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>-7.8863610716508e-11</t>
+          <t>2.43420359260379e-23</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2770,16 +3072,52 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>BP_3_0</t>
+          <t>BP_2_0</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
+          <t>-1.4481394778316e-05</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>BP_2_1</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>-7.8863610716508e-11</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>SIP distortion coefficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>BP_3_0</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr">
+        <is>
           <t>1.4166460599018e-23</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>SIP distortion coefficient</t>
         </is>
@@ -2914,7 +3252,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3120,12 +3458,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mN90oL70mL70mL70</t>
+          <t>ZojVfmgSZmgSdmgS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2025-12-31T11:13:55</t>
+          <t>HDU checksum updated 2026-01-07T16:22:35</t>
         </is>
       </c>
     </row>
@@ -3138,12 +3476,12 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>859190318</t>
+          <t>2339345775</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2025-12-31T11:13:55</t>
+          <t>data unit checksum updated 2026-01-07T16:22:35</t>
         </is>
       </c>
     </row>
@@ -3158,7 +3496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3191,17 +3529,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IMAGE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IMAGE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Image extension</t>
+          <t>binary table extension</t>
         </is>
       </c>
     </row>
@@ -3213,12 +3551,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3258,10 +3596,14 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1024</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of dimension 1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3272,10 +3614,14 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1024</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length of dimension 2</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3291,7 +3637,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of parameters</t>
+          <t>number of group parameters</t>
         </is>
       </c>
     </row>
@@ -3316,35 +3662,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BSCALE</t>
+          <t>TFIELDS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>number of table fields</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BZERO</t>
+          <t>TTYPE1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>32768</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>32768</t>
+          <t>JD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -3352,22 +3702,180 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>TFORM1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>TTYPE2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>RightAscension</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>RightAscension</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TFORM2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TTYPE3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Declination</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Declination</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TFORM3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TTYPE4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rotation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Rotation</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TFORM4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>EXTNAME</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>extension name</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ASTROMETRY</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ASTROMETRY</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Zq3Gho3GZo3Gfo3G</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-07T16:22:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-07T16:22:35</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3415,17 +3923,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>binary table extension</t>
+          <t>Image extension</t>
         </is>
       </c>
     </row>
@@ -3437,17 +3945,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>array data type</t>
+          <t>data type of original image</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3977,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>number of array dimensions</t>
+          <t>dimension of original image</t>
         </is>
       </c>
     </row>
@@ -3482,12 +3990,12 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>length of dimension 1</t>
+          <t>length of original image axis</t>
         </is>
       </c>
     </row>
@@ -3500,12 +4008,12 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>length of dimension 2</t>
+          <t>length of original image axis</t>
         </is>
       </c>
     </row>
@@ -3523,7 +4031,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of group parameters</t>
+          <t>number of parameters</t>
         </is>
       </c>
     </row>
@@ -3548,39 +4056,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TFIELDS</t>
+          <t>BSCALE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>number of table fields</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TTYPE1</t>
+          <t>BZERO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>32768</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>32768</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -3588,506 +4092,60 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TFORM1</t>
+          <t>EXTNAME</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TTYPE2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>DDbmD9ZkDAakD9Yk</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-07T16:22:35</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TFORM2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TTYPE3</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>source_id</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>source_id</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TFORM3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>19A</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>19A</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TTYPE4</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>phot_g_mean_flux</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>phot_g_mean_flux</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TFORM4</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TTYPE5</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>phot_bp_mean_flux</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>phot_bp_mean_flux</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>TFORM5</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>TTYPE6</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>phot_rp_mean_flux</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>phot_rp_mean_flux</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TFORM6</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>TTYPE7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>j_flux</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>j_flux</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>TFORM7</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>TTYPE8</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>h_flux</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>h_flux</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>TFORM8</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>TTYPE9</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>k_flux</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>k_flux</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>TFORM9</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>TTYPE10</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>teff_gspphot</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>teff_gspphot</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>TFORM10</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>TTYPE11</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>row</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>row</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>TFORM11</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>TTYPE12</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>TFORM12</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>TTYPE13</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>row0</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>row0</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>TFORM13</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>TTYPE14</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>column0</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>column0</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>TFORM14</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>262148</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-07T16:22:35</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4100,7 +4158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4133,17 +4191,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IMAGE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IMAGE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Image extension</t>
+          <t>binary table extension</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4213,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-64</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-64</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -4177,12 +4235,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -4200,10 +4258,14 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of dimension 1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4214,116 +4276,628 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length of dimension 2</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NAXIS3</t>
+          <t>PCOUNT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>number of group parameters</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PCOUNT</t>
+          <t>GCOUNT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>number of parameters</t>
+          <t>number of groups</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GCOUNT</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>TFIELDS</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>number of groups</t>
+          <t>number of table fields</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EXTNAME</t>
+          <t>TTYPE1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PRF_MODEL</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PRF_MODEL</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>extension name</t>
-        </is>
-      </c>
+          <t>RA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DPOS0</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>TFORM1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Change in position in Row from original WCS.</t>
-        </is>
-      </c>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DPOS1</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>TTYPE2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Change in position in Column from original WCS.</t>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>TFORM2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TTYPE3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>source_id</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>source_id</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TFORM3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>19A</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>19A</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TTYPE4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>phot_g_mean_flux</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>phot_g_mean_flux</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TFORM4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TTYPE5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>phot_bp_mean_flux</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>phot_bp_mean_flux</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TFORM5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TTYPE6</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>phot_rp_mean_flux</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>phot_rp_mean_flux</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TFORM6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TTYPE7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>j_flux</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>j_flux</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TFORM7</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TTYPE8</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>h_flux</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_flux</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TFORM8</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TTYPE9</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>k_flux</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>k_flux</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TFORM9</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TTYPE10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>teff_gspphot</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>teff_gspphot</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TFORM10</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TTYPE11</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TFORM11</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TTYPE12</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TFORM12</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TTYPE13</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>row0</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>row0</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TFORM13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TTYPE14</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>column0</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>column0</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TFORM14</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CATALOG</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CATALOG</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>GGiDHDgBGDgBGDgB</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-07T16:22:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1448980988</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-07T16:22:35</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4393,17 +4967,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>array data type</t>
+          <t>data type of original image</t>
         </is>
       </c>
     </row>
@@ -4415,17 +4989,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>number of array dimensions</t>
+          <t>dimension of original image</t>
         </is>
       </c>
     </row>
@@ -4438,10 +5012,14 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1024</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4452,79 +5030,369 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1024</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PCOUNT</t>
+          <t>NAXIS3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of parameters</t>
+          <t>length of original image axis</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCOUNT</t>
+          <t>PCOUNT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>number of groups</t>
+          <t>number of parameters</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>APERTURE</t>
-        </is>
-      </c>
+          <t>GCOUNT</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>APERTURE</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>extension name</t>
+          <t>number of groups</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PRF_MODEL</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PRF_MODEL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>DPOS0</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Change in position in Row from original WCS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DPOS1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Change in position in Column from original WCS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Tr6cUo6aTo6aTo6a</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-07T16:22:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3766554851</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-07T16:22:35</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Fixed Value</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Example Value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>XTENSION</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>IMAGE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Image extension</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BITPIX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>data type of original image</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NAXIS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>dimension of original image</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NAXIS1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NAXIS2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>length of original image axis</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PCOUNT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>number of parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GCOUNT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>number of groups</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>APERTURE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>APERTURE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>CONTAM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0029941333932875618</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4542,7 +5410,7 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.7662145070518919</t>
+          <t>0.6605542195229007</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4560,7 +5428,7 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>241900.552580801</t>
+          <t>3783.2271792142883</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4578,7 +5446,7 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>45.46136014093954</t>
+          <t>359.9895608184272</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -4592,7 +5460,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-16.595271506306272</t>
+          <t>0.012162614450386506</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -4606,7 +5474,7 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1023.0654840847828</t>
+          <t>1034.9461994334877</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -4620,7 +5488,7 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1025.0327875137618</t>
+          <t>950.0063201028894</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -4634,7 +5502,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5153091836072107136</t>
+          <t>2738188646457069696</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -4708,6 +5576,42 @@
       <c r="D21" t="inlineStr">
         <is>
           <t>Corner of the image in COLUMN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>jikDmik9jikAjik9</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-07T16:22:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1048592</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-07T16:22:35</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level2-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level2-ffi_visda.xlsx
@@ -818,12 +818,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ZplUfmkRZmkRdmkR</t>
+          <t>ZolTemjRZmjRbmjR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:35</t>
+          <t>HDU checksum updated 2026-01-07T18:03:56</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:35</t>
+          <t>data unit checksum updated 2026-01-07T18:03:56</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1512,12 +1512,12 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>aCRLc9PLaAPLa9PL</t>
+          <t>BVGqDVFnBVFnBVFn</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:34</t>
+          <t>HDU checksum updated 2026-01-07T18:03:55</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:34</t>
+          <t>data unit checksum updated 2026-01-07T18:03:55</t>
         </is>
       </c>
     </row>
@@ -1610,41 +1610,49 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PFCLASS</t>
+          <t>DPCOBSID</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>VISDAFFILevel2HDUList</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>DPC Observation ID</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GAIA_ID</t>
+          <t>SEQSTART</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2738188646457069696</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>DPC Observation Sequence Start</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>PFCLASS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cast data to float.</t>
+          <t>VISDAFFILevel2HDUList</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -1652,13 +1660,13 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>GAIA_ID</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Applied bias.</t>
+          <t>2738188646457069696</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -1672,7 +1680,7 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Applied dark.</t>
+          <t>Cast data to float.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1686,7 +1694,7 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Applied flat.</t>
+          <t>Applied bias.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1700,7 +1708,7 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Applied gain.</t>
+          <t>Applied dark.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1714,10 +1722,38 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
+          <t>Applied flat.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Applied gain.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
           <t>Appended WCS.</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1930,12 +1966,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9aGCEX9B9aGBCU9B</t>
+          <t>9aFDDV9A9aEAAU9A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:34</t>
+          <t>HDU checksum updated 2026-01-07T18:03:56</t>
         </is>
       </c>
     </row>
@@ -1953,7 +1989,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:34</t>
+          <t>data unit checksum updated 2026-01-07T18:03:56</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3494,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ZojVfmgSZmgSdmgS</t>
+          <t>ZngUemgSZmgSbmgS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:35</t>
+          <t>HDU checksum updated 2026-01-07T18:03:56</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3517,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:35</t>
+          <t>data unit checksum updated 2026-01-07T18:03:56</t>
         </is>
       </c>
     </row>
@@ -3852,12 +3888,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Zq3Gho3GZo3Gfo3G</t>
+          <t>Zp3Igo2FZo2Fdo2F</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:35</t>
+          <t>HDU checksum updated 2026-01-07T18:03:56</t>
         </is>
       </c>
     </row>
@@ -3875,7 +3911,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:35</t>
+          <t>data unit checksum updated 2026-01-07T18:03:56</t>
         </is>
       </c>
     </row>
@@ -4120,12 +4156,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DDbmD9ZkDAakD9Yk</t>
+          <t>CCalD9ZkCAakC9Wk</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:35</t>
+          <t>HDU checksum updated 2026-01-07T18:03:56</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4179,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:35</t>
+          <t>data unit checksum updated 2026-01-07T18:03:56</t>
         </is>
       </c>
     </row>
@@ -4874,12 +4910,12 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>GGiDHDgBGDgBGDgB</t>
+          <t>FIjEIIhBFIhBFIhB</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:35</t>
+          <t>HDU checksum updated 2026-01-07T18:03:56</t>
         </is>
       </c>
     </row>
@@ -4892,12 +4928,12 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1448980988</t>
+          <t>1246934529</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:35</t>
+          <t>data unit checksum updated 2026-01-07T18:03:56</t>
         </is>
       </c>
     </row>
@@ -5160,12 +5196,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tr6cUo6aTo6aTo6a</t>
+          <t>TSAGTP7DTPADTP7D</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:35</t>
+          <t>HDU checksum updated 2026-01-07T18:03:56</t>
         </is>
       </c>
     </row>
@@ -5178,12 +5214,12 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3766554851</t>
+          <t>1566935263</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:35</t>
+          <t>data unit checksum updated 2026-01-07T18:03:56</t>
         </is>
       </c>
     </row>
@@ -5410,7 +5446,7 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.6605542195229007</t>
+          <t>0.6605542195229065</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5428,7 +5464,7 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3783.2271792142883</t>
+          <t>3783.2271792143215</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5460,7 +5496,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.012162614450386506</t>
+          <t>0.012162614450386505</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -5488,7 +5524,7 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>950.0063201028894</t>
+          <t>950.0063201028892</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -5588,12 +5624,12 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jikDmik9jikAjik9</t>
+          <t>kikBmik9kikAkik9</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T16:22:35</t>
+          <t>HDU checksum updated 2026-01-07T18:03:56</t>
         </is>
       </c>
     </row>
@@ -5611,7 +5647,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T16:22:35</t>
+          <t>data unit checksum updated 2026-01-07T18:03:56</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level2-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level2-ffi_visda.xlsx
@@ -818,12 +818,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ZolTemjRZmjRbmjR</t>
+          <t>ZrkWdojTZojTbojT</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:56</t>
+          <t>HDU checksum updated 2026-01-08T14:08:01</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:56</t>
+          <t>data unit checksum updated 2026-01-08T14:08:01</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1512,12 +1512,12 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BVGqDVFnBVFnBVFn</t>
+          <t>QhIZQhIXQhIXQhIX</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:55</t>
+          <t>HDU checksum updated 2026-01-08T14:08:00</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:55</t>
+          <t>data unit checksum updated 2026-01-08T14:08:00</t>
         </is>
       </c>
     </row>
@@ -1634,7 +1634,7 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2454833</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1660,27 +1660,31 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GAIA_ID</t>
+          <t>PFTIME</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2738188646457069696</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>2026-01-08T19:08:00.144</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Pandora DPC Processing Time</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>COMMENT</t>
+          <t>GAIA_ID</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cast data to float.</t>
+          <t>2738188646457069696</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -1694,7 +1698,7 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Applied bias.</t>
+          <t>Cast data to float.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -1708,7 +1712,7 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Applied dark.</t>
+          <t>Applied bias.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -1722,7 +1726,7 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Applied flat.</t>
+          <t>Applied dark.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -1736,7 +1740,7 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Applied gain.</t>
+          <t>Applied flat.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -1750,10 +1754,24 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
+          <t>Applied gain.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>COMMENT</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
           <t>Appended WCS.</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1966,12 +1984,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9aFDDV9A9aEAAU9A</t>
+          <t>9cEECZ9D9aEDAY9D</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:56</t>
+          <t>HDU checksum updated 2026-01-08T14:08:00</t>
         </is>
       </c>
     </row>
@@ -1989,7 +2007,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:56</t>
+          <t>data unit checksum updated 2026-01-08T14:08:00</t>
         </is>
       </c>
     </row>
@@ -3494,12 +3512,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ZngUemgSZmgSbmgS</t>
+          <t>ZqiXdofUZofUbofU</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:56</t>
+          <t>HDU checksum updated 2026-01-08T14:08:01</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3535,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:56</t>
+          <t>data unit checksum updated 2026-01-08T14:08:01</t>
         </is>
       </c>
     </row>
@@ -3888,12 +3906,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Zp3Igo2FZo2Fdo2F</t>
+          <t>Z32Ig12IZ12Id12I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:56</t>
+          <t>HDU checksum updated 2026-01-08T14:08:01</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3929,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:56</t>
+          <t>data unit checksum updated 2026-01-08T14:08:01</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4174,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CCalD9ZkCAakC9Wk</t>
+          <t>CHaoC9YmCEamC9Wm</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:56</t>
+          <t>HDU checksum updated 2026-01-08T14:08:01</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4197,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:56</t>
+          <t>data unit checksum updated 2026-01-08T14:08:01</t>
         </is>
       </c>
     </row>
@@ -4910,12 +4928,12 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FIjEIIhBFIhBFIhB</t>
+          <t>6QAa8N5Y6NAa6N5W</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:56</t>
+          <t>HDU checksum updated 2026-01-08T14:08:01</t>
         </is>
       </c>
     </row>
@@ -4928,12 +4946,12 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1246934529</t>
+          <t>1090674493</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:56</t>
+          <t>data unit checksum updated 2026-01-08T14:08:01</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5214,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TSAGTP7DTPADTP7D</t>
+          <t>7LIWBKIW9KIWAKIW</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:56</t>
+          <t>HDU checksum updated 2026-01-08T14:08:01</t>
         </is>
       </c>
     </row>
@@ -5214,12 +5232,12 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1566935263</t>
+          <t>2117356093</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:56</t>
+          <t>data unit checksum updated 2026-01-08T14:08:01</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5464,7 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.6605542195229065</t>
+          <t>0.6804319579252933</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5464,7 +5482,7 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3783.2271792143215</t>
+          <t>3897.074003536385</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5482,7 +5500,7 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>359.9895608184272</t>
+          <t>359.98956765457893</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -5496,7 +5514,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.012162614450386505</t>
+          <t>0.01225927433994913</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -5510,7 +5528,7 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1034.9461994334877</t>
+          <t>1035.3073573208812</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -5524,7 +5542,7 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>950.0063201028892</t>
+          <t>949.743697350043</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -5624,12 +5642,12 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>kikBmik9kikAkik9</t>
+          <t>ed7EhZ6Beb6BeZ6B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-07T18:03:56</t>
+          <t>HDU checksum updated 2026-01-08T14:08:01</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5660,12 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1048592</t>
+          <t>1048594</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-07T18:03:56</t>
+          <t>data unit checksum updated 2026-01-08T14:08:01</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level2-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level2-ffi_visda.xlsx
@@ -818,12 +818,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ZrkWdojTZojTbojT</t>
+          <t>a1oVb0lUa0lUa0lU</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:08:01</t>
+          <t>HDU checksum updated 2026-01-16T10:20:00</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:08:01</t>
+          <t>data unit checksum updated 2026-01-16T10:20:00</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1512,12 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>QhIZQhIXQhIXQhIX</t>
+          <t>ZihHZfgHZfgHZfgH</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:08:00</t>
+          <t>HDU checksum updated 2026-01-16T10:19:59</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:08:00</t>
+          <t>data unit checksum updated 2026-01-16T10:19:59</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DPCOBSID</t>
+          <t>DPCSEQID</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DPC Observation ID</t>
+          <t>DPC Obseravation Sequence ID</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1666,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-01-08T19:08:00.144</t>
+          <t>2026-01-16T17:19:59.383</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1984,12 +1984,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9cEECZ9D9aEDAY9D</t>
+          <t>9bCFGZAD9bADGZAD</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:08:00</t>
+          <t>HDU checksum updated 2026-01-16T10:20:00</t>
         </is>
       </c>
     </row>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:08:00</t>
+          <t>data unit checksum updated 2026-01-16T10:20:00</t>
         </is>
       </c>
     </row>
@@ -3512,12 +3512,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ZqiXdofUZofUbofU</t>
+          <t>a0jWb0iVa0iVa0iV</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:08:01</t>
+          <t>HDU checksum updated 2026-01-16T10:20:00</t>
         </is>
       </c>
     </row>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:08:01</t>
+          <t>data unit checksum updated 2026-01-16T10:20:00</t>
         </is>
       </c>
     </row>
@@ -3906,12 +3906,12 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Z32Ig12IZ12Id12I</t>
+          <t>b26Kc24Ib24Ib24I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:08:01</t>
+          <t>HDU checksum updated 2026-01-16T10:20:00</t>
         </is>
       </c>
     </row>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:08:01</t>
+          <t>data unit checksum updated 2026-01-16T10:20:00</t>
         </is>
       </c>
     </row>
@@ -4174,12 +4174,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CHaoC9YmCEamC9Wm</t>
+          <t>EHdnG9ZnEGdnE9Zn</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:08:01</t>
+          <t>HDU checksum updated 2026-01-16T10:20:00</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:08:01</t>
+          <t>data unit checksum updated 2026-01-16T10:20:00</t>
         </is>
       </c>
     </row>
@@ -4928,12 +4928,12 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>6QAa8N5Y6NAa6N5W</t>
+          <t>9PCa9O9Y9OAa9O9Y</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:08:01</t>
+          <t>HDU checksum updated 2026-01-16T10:20:00</t>
         </is>
       </c>
     </row>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:08:01</t>
+          <t>data unit checksum updated 2026-01-16T10:20:00</t>
         </is>
       </c>
     </row>
@@ -5214,12 +5214,12 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7LIWBKIW9KIWAKIW</t>
+          <t>9NMYFKKW9KKWEKKW</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:08:01</t>
+          <t>HDU checksum updated 2026-01-16T10:20:00</t>
         </is>
       </c>
     </row>
@@ -5237,7 +5237,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:08:01</t>
+          <t>data unit checksum updated 2026-01-16T10:20:00</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ed7EhZ6Beb6BeZ6B</t>
+          <t>hdADiZ2Chd8ChZ8C</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-08T14:08:01</t>
+          <t>HDU checksum updated 2026-01-16T10:20:00</t>
         </is>
       </c>
     </row>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-08T14:08:01</t>
+          <t>data unit checksum updated 2026-01-16T10:20:00</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level2-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level2-ffi_visda.xlsx
@@ -16,7 +16,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext5" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext6" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext7" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ext8" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,12 +501,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ASTROMETRY</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BinTableHDU</t>
+          <t>CompImageHDU</t>
         </is>
       </c>
       <c r="C5" t="b">
@@ -517,12 +516,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>CATALOG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CompImageHDU</t>
+          <t>BinTableHDU</t>
         </is>
       </c>
       <c r="C6" t="b">
@@ -532,12 +531,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CATALOG</t>
+          <t>PRF_MODEL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BinTableHDU</t>
+          <t>CompImageHDU</t>
         </is>
       </c>
       <c r="C7" t="b">
@@ -547,7 +546,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PRF_MODEL</t>
+          <t>APERTURE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -562,287 +561,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>APERTURE</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CompImageHDU</t>
+          <t>ImageHDU</t>
         </is>
       </c>
       <c r="C9" t="b">
         <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ImageHDU</t>
-        </is>
-      </c>
-      <c r="C10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Fixed Value</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Example Value</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>XTENSION</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IMAGE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>IMAGE</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Image extension</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>BITPIX</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>-64</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>-64</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>array data type</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NAXIS</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>number of array dimensions</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NAXIS1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1024</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NAXIS2</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1024</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NAXIS3</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>PCOUNT</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>number of parameters</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>GCOUNT</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>number of groups</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>UNIT</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>electrons/pixel</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>data units: electrons/pixel</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>extension name</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>a1oVb0lUa0lUa0lU</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T10:20:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>606763591</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T10:20:00</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -1512,12 +1240,12 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ZihHZfgHZfgHZfgH</t>
+          <t>YkjLchjIZhjIahjI</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:19:59</t>
+          <t>HDU checksum updated 2026-01-16T15:40:12</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1263,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:19:59</t>
+          <t>data unit checksum updated 2026-01-16T15:40:12</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1394,7 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-01-16T17:19:59.383</t>
+          <t>2026-01-16T22:40:12.639</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1984,12 +1712,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>9bCFGZAD9bADGZAD</t>
+          <t>9aBBHWAB9aABEUAB</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:20:00</t>
+          <t>HDU checksum updated 2026-01-16T15:40:13</t>
         </is>
       </c>
     </row>
@@ -2007,7 +1735,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:20:00</t>
+          <t>data unit checksum updated 2026-01-16T15:40:13</t>
         </is>
       </c>
     </row>
@@ -3512,12 +3240,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>a0jWb0iVa0iVa0iV</t>
+          <t>ZoiVimiSZmiSfmiS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-01-16T10:20:00</t>
+          <t>HDU checksum updated 2026-01-16T15:40:13</t>
         </is>
       </c>
     </row>
@@ -3535,7 +3263,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-01-16T10:20:00</t>
+          <t>data unit checksum updated 2026-01-16T15:40:13</t>
         </is>
       </c>
     </row>
@@ -3550,7 +3278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3583,17 +3311,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>binary table extension</t>
+          <t>Image extension</t>
         </is>
       </c>
     </row>
@@ -3605,17 +3333,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>array data type</t>
+          <t>data type of original image</t>
         </is>
       </c>
     </row>
@@ -3637,7 +3365,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>number of array dimensions</t>
+          <t>dimension of original image</t>
         </is>
       </c>
     </row>
@@ -3650,12 +3378,12 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>length of dimension 1</t>
+          <t>length of original image axis</t>
         </is>
       </c>
     </row>
@@ -3668,12 +3396,12 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>length of dimension 2</t>
+          <t>length of original image axis</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3419,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of group parameters</t>
+          <t>number of parameters</t>
         </is>
       </c>
     </row>
@@ -3716,39 +3444,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TFIELDS</t>
+          <t>BSCALE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>number of table fields</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TTYPE1</t>
+          <t>BZERO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>32768</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>JD</t>
+          <t>32768</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -3756,180 +3480,58 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TFORM1</t>
+          <t>EXTNAME</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>QUALITY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>QUALITY</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TTYPE2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>RightAscension</t>
-        </is>
-      </c>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RightAscension</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>EDemF9ZkEAbkE9Zk</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-16T15:40:13</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TFORM2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TTYPE3</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Declination</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Declination</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TFORM3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TTYPE4</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Rotation</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TFORM4</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>ASTROMETRY</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>ASTROMETRY</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>b26Kc24Ib24Ib24I</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T10:20:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T10:20:00</t>
+          <t>262148</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-16T15:40:13</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3977,17 +3579,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>IMAGE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>IMAGE</t>
+          <t>BINTABLE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Image extension</t>
+          <t>binary table extension</t>
         </is>
       </c>
     </row>
@@ -3999,17 +3601,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>data type of original image</t>
+          <t>array data type</t>
         </is>
       </c>
     </row>
@@ -4031,7 +3633,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>dimension of original image</t>
+          <t>number of array dimensions</t>
         </is>
       </c>
     </row>
@@ -4044,12 +3646,12 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>123</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>length of original image axis</t>
+          <t>length of dimension 1</t>
         </is>
       </c>
     </row>
@@ -4062,12 +3664,12 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>length of original image axis</t>
+          <t>length of dimension 2</t>
         </is>
       </c>
     </row>
@@ -4085,7 +3687,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of parameters</t>
+          <t>number of group parameters</t>
         </is>
       </c>
     </row>
@@ -4110,35 +3712,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BSCALE</t>
+          <t>TFIELDS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>number of table fields</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BZERO</t>
+          <t>TTYPE1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>32768</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>32768</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -4146,58 +3752,540 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EXTNAME</t>
+          <t>TFORM1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>QUALITY</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>QUALITY</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>extension name</t>
-        </is>
-      </c>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
+          <t>TTYPE2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dec</t>
+        </is>
+      </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>EHdnG9ZnEGdnE9Zn</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T10:20:00</t>
-        </is>
-      </c>
+          <t>Dec</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>TFORM2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>TTYPE3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>source_id</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>source_id</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TFORM3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>19A</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>19A</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TTYPE4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>phot_g_mean_flux</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>phot_g_mean_flux</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TFORM4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TTYPE5</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>phot_bp_mean_flux</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>phot_bp_mean_flux</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>TFORM5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>TTYPE6</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>phot_rp_mean_flux</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>phot_rp_mean_flux</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>TFORM6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>TTYPE7</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>j_flux</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>j_flux</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TFORM7</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TTYPE8</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>h_flux</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_flux</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>TFORM8</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TTYPE9</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>k_flux</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>k_flux</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TFORM9</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TTYPE10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>teff_gspphot</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>teff_gspphot</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TFORM10</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TTYPE11</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>row</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TFORM11</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TTYPE12</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TFORM12</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TTYPE13</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>row0</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>row0</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>TFORM13</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>TTYPE14</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>column0</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>column0</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>TFORM14</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CATALOG</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CATALOG</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>8OBaAL9U2LAZ8L9Z</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-16T15:40:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>DATASUM</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>262148</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T10:20:00</t>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1090674493</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-16T15:40:13</t>
         </is>
       </c>
     </row>
@@ -4212,7 +4300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4245,17 +4333,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BINTABLE</t>
+          <t>IMAGE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>binary table extension</t>
+          <t>Image extension</t>
         </is>
       </c>
     </row>
@@ -4267,17 +4355,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>array data type</t>
+          <t>data type of original image</t>
         </is>
       </c>
     </row>
@@ -4289,17 +4377,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>number of array dimensions</t>
+          <t>dimension of original image</t>
         </is>
       </c>
     </row>
@@ -4312,12 +4400,12 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>length of dimension 1</t>
+          <t>length of original image axis</t>
         </is>
       </c>
     </row>
@@ -4330,628 +4418,160 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>32</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>length of dimension 2</t>
+          <t>length of original image axis</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PCOUNT</t>
+          <t>NAXIS3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>number of group parameters</t>
+          <t>length of original image axis</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCOUNT</t>
+          <t>PCOUNT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>number of groups</t>
+          <t>number of parameters</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TFIELDS</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>GCOUNT</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>number of table fields</t>
+          <t>number of groups</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TTYPE1</t>
+          <t>EXTNAME</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>PRF_MODEL</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>PRF_MODEL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>extension name</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TFORM1</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
+          <t>DPOS0</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Change in position in Row from original WCS.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TTYPE2</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Dec</t>
-        </is>
-      </c>
+          <t>DPOS1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dec</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Change in position in Column from original WCS.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TFORM2</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>9JLUEIKU9IKUEIKU</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-16T15:40:13</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TTYPE3</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>source_id</t>
-        </is>
-      </c>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>source_id</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TFORM3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>19A</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>19A</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>TTYPE4</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>phot_g_mean_flux</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>phot_g_mean_flux</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TFORM4</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TTYPE5</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>phot_bp_mean_flux</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>phot_bp_mean_flux</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>TFORM5</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>TTYPE6</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>phot_rp_mean_flux</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>phot_rp_mean_flux</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>TFORM6</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>TTYPE7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>j_flux</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>j_flux</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>TFORM7</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>TTYPE8</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>h_flux</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>h_flux</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>TFORM8</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>TTYPE9</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>k_flux</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>k_flux</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>TFORM9</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>TTYPE10</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>teff_gspphot</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>teff_gspphot</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>TFORM10</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>TTYPE11</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>row</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>row</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>TFORM11</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>TTYPE12</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>column</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>TFORM12</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>TTYPE13</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>row0</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>row0</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>TFORM13</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>TTYPE14</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>column0</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>column0</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>TFORM14</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>K</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>CATALOG</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>9PCa9O9Y9OAa9O9Y</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T10:20:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1090674493</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T10:20:00</t>
+          <t>2117356093</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-16T15:40:13</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5021,12 +4641,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-64</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-64</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -5043,12 +4663,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -5066,7 +4686,7 @@
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -5084,7 +4704,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -5096,148 +4716,290 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NAXIS3</t>
+          <t>PCOUNT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>length of original image axis</t>
+          <t>number of parameters</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PCOUNT</t>
+          <t>GCOUNT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>number of parameters</t>
+          <t>number of groups</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>GCOUNT</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>APERTURE</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>APERTURE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>number of groups</t>
+          <t>extension name</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>PRF_MODEL</t>
-        </is>
-      </c>
+          <t>CONTAM</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PRF_MODEL</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>extension name</t>
+          <t>Flux not from the target in aperture in e/s</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DPOS0</t>
+          <t>COMPLTE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.6804319579252933</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Change in position in Row from original WCS.</t>
+          <t>Fraction of flux from the target in aperture</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DPOS1</t>
+          <t>TOTAP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3897.074003536385</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Change in position in Column from original WCS.</t>
+          <t>Total flux expected in aperture in e/s</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CHECKSUM</t>
+          <t>RA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9NMYFKKW9KKWEKKW</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T10:20:00</t>
-        </is>
-      </c>
+          <t>359.98956765457893</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DATASUM</t>
+          <t>DEC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2117356093</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T10:20:00</t>
+          <t>0.01225927433994913</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ROW</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1035.3073573208812</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>COLUMN</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>949.743697350043</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>GAIA_ID</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2738188646457069696</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>IMSIZE0</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Size of the full detector image in ROW</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>IMCRNR0</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Corner of the image in ROW.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>IMSIZE1</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1024</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Size of the full detector image in COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>IMCRNR1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>512</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Corner of the image in COLUMN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CHECKSUM</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>haAJhY19ha8GhW89</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>HDU checksum updated 2026-01-16T15:40:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DATASUM</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1048594</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-16T15:40:13</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5307,17 +5069,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>data type of original image</t>
+          <t>array data type</t>
         </is>
       </c>
     </row>
@@ -5329,17 +5091,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>dimension of original image</t>
+          <t>number of array dimensions</t>
         </is>
       </c>
     </row>
@@ -5355,11 +5117,7 @@
           <t>1024</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>length of original image axis</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5373,299 +5131,131 @@
           <t>1024</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>length of original image axis</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PCOUNT</t>
+          <t>NAXIS3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>number of parameters</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GCOUNT</t>
+          <t>PCOUNT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>number of groups</t>
+          <t>number of parameters</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EXTNAME</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>APERTURE</t>
-        </is>
-      </c>
+          <t>GCOUNT</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>APERTURE</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>extension name</t>
+          <t>number of groups</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CONTAM</t>
+          <t>UNIT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>electrons/pixel</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Flux not from the target in aperture in e/s</t>
+          <t>data units: electrons/pixel</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COMPLTE</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>EXTNAME</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.6804319579252933</t>
+          <t>ERROR</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Fraction of flux from the target in aperture</t>
+          <t>extension name</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TOTAP</t>
+          <t>CHECKSUM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3897.074003536385</t>
+          <t>ZpnUimlRZmlRfmlR</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Total flux expected in aperture in e/s</t>
+          <t>HDU checksum updated 2026-01-16T15:40:13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RA</t>
+          <t>DATASUM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>359.98956765457893</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>DEC</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>0.01225927433994913</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ROW</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1035.3073573208812</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>COLUMN</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>949.743697350043</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>GAIA_ID</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>2738188646457069696</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>IMSIZE0</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1024</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Size of the full detector image in ROW</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>IMCRNR0</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Corner of the image in ROW.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>IMSIZE1</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1024</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Size of the full detector image in COLUMN</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>IMCRNR1</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>512</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Corner of the image in COLUMN.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>CHECKSUM</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>hdADiZ2Chd8ChZ8C</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>HDU checksum updated 2026-01-16T10:20:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>DATASUM</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1048594</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>data unit checksum updated 2026-01-16T10:20:00</t>
+          <t>606763591</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>data unit checksum updated 2026-01-16T15:40:13</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level2-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level2-ffi_visda.xlsx
@@ -1208,12 +1208,12 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>6YAq6W2o6W8o6W8o</t>
+          <t>5XAq6V2o5V8o5V8o</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:36</t>
+          <t>HDU checksum updated 2026-09-08T14:41:36</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:36</t>
+          <t>data unit checksum updated 2026-09-08T14:41:36</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-26T01:26:36.380</t>
+          <t>2026-09-08T18:41:36.460</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1544,12 +1544,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dKhBeJZAdJfAdJZA</t>
+          <t>eJbHeIa9eIaGeIa9</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:37</t>
+          <t>HDU checksum updated 2026-09-08T14:41:37</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:37</t>
+          <t>data unit checksum updated 2026-09-08T14:41:37</t>
         </is>
       </c>
     </row>
@@ -1932,12 +1932,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mJ7qmJ7omJ7omJ7o</t>
+          <t>mIAppI0nmI7nmI7n</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:37</t>
+          <t>HDU checksum updated 2026-09-08T14:41:37</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:37</t>
+          <t>data unit checksum updated 2026-09-08T14:41:37</t>
         </is>
       </c>
     </row>
@@ -2160,12 +2160,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2efA2Zc82dcA2Zc7</t>
+          <t>2cfA5Zd62bdA2Zd5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:37</t>
+          <t>HDU checksum updated 2026-09-08T14:41:37</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:37</t>
+          <t>data unit checksum updated 2026-09-08T14:41:37</t>
         </is>
       </c>
     </row>
@@ -2388,12 +2388,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bAJab1JWb8Jab8JU</t>
+          <t>b9Mae7JUb7JZb7JZ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:37</t>
+          <t>HDU checksum updated 2026-09-08T14:41:37</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:37</t>
+          <t>data unit checksum updated 2026-09-08T14:41:37</t>
         </is>
       </c>
     </row>
@@ -2656,12 +2656,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ZhHVgf9TZfGTff9T</t>
+          <t>agAUaeASaeASaeAS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-08-25T21:26:37</t>
+          <t>HDU checksum updated 2026-09-08T14:41:37</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-08-25T21:26:37</t>
+          <t>data unit checksum updated 2026-09-08T14:41:37</t>
         </is>
       </c>
     </row>

--- a/src/pandorafits/formats/visda/level2-ffi_visda.xlsx
+++ b/src/pandorafits/formats/visda/level2-ffi_visda.xlsx
@@ -1208,12 +1208,12 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5XAq6V2o5V8o5V8o</t>
+          <t>5X9p5W8n5W8n5W8n</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:36</t>
+          <t>HDU checksum updated 2026-09-09T15:46:14</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:36</t>
+          <t>data unit checksum updated 2026-09-09T15:46:14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-09-08T18:41:36.460</t>
+          <t>2026-09-09T19:46:14.050</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1544,12 +1544,12 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>eJbHeIa9eIaGeIa9</t>
+          <t>dKgIdIZ9dIfGdIZ9</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:37</t>
+          <t>HDU checksum updated 2026-09-09T15:46:15</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:37</t>
+          <t>data unit checksum updated 2026-09-09T15:46:15</t>
         </is>
       </c>
     </row>
@@ -1932,12 +1932,12 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>mIAppI0nmI7nmI7n</t>
+          <t>lJ9qoI6nlI6nlI6n</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:37</t>
+          <t>HDU checksum updated 2026-09-09T15:46:15</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:37</t>
+          <t>data unit checksum updated 2026-09-09T15:46:15</t>
         </is>
       </c>
     </row>
@@ -2160,12 +2160,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2cfA5Zd62bdA2Zd5</t>
+          <t>1deA4Zc71bcA1Zc5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:37</t>
+          <t>HDU checksum updated 2026-09-09T15:46:15</t>
         </is>
       </c>
     </row>
@@ -2183,7 +2183,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:37</t>
+          <t>data unit checksum updated 2026-09-09T15:46:15</t>
         </is>
       </c>
     </row>
@@ -2388,12 +2388,12 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>b9Mae7JUb7JZb7JZ</t>
+          <t>aALad0IVa7IZa7IZ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:37</t>
+          <t>HDU checksum updated 2026-09-09T15:46:15</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:37</t>
+          <t>data unit checksum updated 2026-09-09T15:46:15</t>
         </is>
       </c>
     </row>
@@ -2656,12 +2656,12 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>agAUaeASaeASaeAS</t>
+          <t>ZhGVfe9SZeGSfe9S</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HDU checksum updated 2026-09-08T14:41:37</t>
+          <t>HDU checksum updated 2026-09-09T15:46:15</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>data unit checksum updated 2026-09-08T14:41:37</t>
+          <t>data unit checksum updated 2026-09-09T15:46:15</t>
         </is>
       </c>
     </row>
